--- a/docs/07-Power-Budget/Power Budget T102 EGR 304.xlsx
+++ b/docs/07-Power-Budget/Power Budget T102 EGR 304.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\austi\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0DDEDA-C48C-4A58-8E1A-319F5A70994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="20775" yWindow="-442" windowWidth="21600" windowHeight="11392" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
   <si>
     <t>Team Number:</t>
   </si>
@@ -115,12 +137,6 @@
     <t>+5V Regulator</t>
   </si>
   <si>
-    <t>LM7805</t>
-  </si>
-  <si>
-    <t>5-35V</t>
-  </si>
-  <si>
     <t>External Power Source 1</t>
   </si>
   <si>
@@ -138,43 +154,88 @@
   <si>
     <t>Total left</t>
   </si>
+  <si>
+    <t>LM1085-5.0</t>
+  </si>
+  <si>
+    <t>6.5-25V</t>
+  </si>
+  <si>
+    <t>AOFT2618L</t>
+  </si>
+  <si>
+    <t>MOSFET</t>
+  </si>
+  <si>
+    <t>0-20V</t>
+  </si>
+  <si>
+    <t>H-Bridge</t>
+  </si>
+  <si>
+    <t>FAN8100N</t>
+  </si>
+  <si>
+    <t>2.2-9V</t>
+  </si>
+  <si>
+    <t>+5V</t>
+  </si>
+  <si>
+    <t>WBEEAB0711Q5B49</t>
+  </si>
+  <si>
+    <t>+12V</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -190,7 +251,13 @@
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -204,6 +271,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -215,6 +283,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -223,6 +293,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -231,58 +304,65 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -472,28 +552,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Y977"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.13"/>
-    <col customWidth="1" min="2" max="2" width="20.38"/>
-    <col customWidth="1" min="4" max="4" width="11.0"/>
-    <col customWidth="1" min="5" max="5" width="9.25"/>
-    <col customWidth="1" min="6" max="6" width="12.38"/>
-    <col customWidth="1" min="7" max="7" width="11.75"/>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="2" width="20.36328125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2">
+        <v>102</v>
+      </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -518,9 +605,13 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -545,9 +636,13 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
     </row>
-    <row r="3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -572,12 +667,12 @@
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>102.0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -603,18 +698,28 @@
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -634,18 +739,27 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>500</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" ref="G6:G11" si="0">E6*F6</f>
+        <v>500</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -665,18 +779,27 @@
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
+    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
       </c>
-      <c r="B7" s="2">
-        <v>1.0</v>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1500</v>
+      </c>
+      <c r="G7" s="4">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -696,27 +819,26 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
+    <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
+      <c r="C8" s="5">
+        <v>2941</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="4" t="s">
+        <v>20</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
+      <c r="E8" s="4">
+        <v>1</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>10</v>
+      <c r="F8" s="4">
+        <v>550</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>12</v>
+      <c r="G8" s="4">
+        <f t="shared" si="0"/>
+        <v>550</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -737,26 +859,25 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
+      <c r="B9" s="4" t="s">
+        <v>45</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>14</v>
+      <c r="C9" s="10" t="s">
+        <v>46</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
+      <c r="D9" s="4" t="s">
+        <v>47</v>
       </c>
-      <c r="E9" s="5">
-        <v>1.0</v>
+      <c r="E9" s="4">
+        <v>1</v>
       </c>
-      <c r="F9" s="5">
-        <v>500.0</v>
+      <c r="F9" s="4">
+        <v>105</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" ref="G9:G12" si="1">E9*F9</f>
-        <v>500</v>
+        <v>105</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -777,26 +898,26 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>16</v>
+      <c r="B10" s="4" t="s">
+        <v>43</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>17</v>
+      <c r="C10" s="4" t="s">
+        <v>42</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>18</v>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
       </c>
-      <c r="E10" s="5">
-        <v>1.0</v>
+      <c r="E10" s="4">
+        <v>1</v>
       </c>
-      <c r="F10" s="5">
-        <v>1500.0</v>
+      <c r="F10" s="4">
+        <v>50</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <f>E10*F10</f>
+        <v>50</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -817,25 +938,25 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="5" t="s">
-        <v>19</v>
+      <c r="B11" s="4" t="s">
+        <v>21</v>
       </c>
-      <c r="C11" s="6">
-        <v>2941.0</v>
+      <c r="C11" s="5">
+        <v>2941</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5">
-        <v>1.0</v>
+      <c r="E11" s="4">
+        <v>1</v>
       </c>
-      <c r="F11" s="5">
-        <v>550.0</v>
+      <c r="F11" s="4">
+        <v>550</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>550</v>
       </c>
       <c r="H11" s="1"/>
@@ -857,26 +978,27 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
-        <v>21</v>
+    <row r="12" spans="1:25" ht="47.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>22</v>
       </c>
-      <c r="C12" s="6">
-        <v>2941.0</v>
+      <c r="B12" s="3" t="s">
+        <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>20</v>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
       </c>
-      <c r="E12" s="5">
-        <v>1.0</v>
+      <c r="D12" s="3" t="s">
+        <v>9</v>
       </c>
-      <c r="F12" s="5">
-        <v>550.0</v>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
       </c>
-      <c r="G12" s="4">
-        <f t="shared" si="1"/>
-        <v>550</v>
+      <c r="F12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -897,27 +1019,26 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>22</v>
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>16</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>7</v>
+      <c r="C13" s="4" t="s">
+        <v>17</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>8</v>
+      <c r="D13" s="4" t="s">
+        <v>18</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>9</v>
+      <c r="E13" s="4">
+        <v>1</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
+      <c r="F13" s="4">
+        <v>1500</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>12</v>
+      <c r="G13" s="4">
+        <f>E13*F13</f>
+        <v>1500</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -938,26 +1059,26 @@
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="5" t="s">
-        <v>16</v>
+      <c r="B14" s="4" t="s">
+        <v>43</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>17</v>
+      <c r="C14" s="4" t="s">
+        <v>42</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>18</v>
+      <c r="D14" s="4" t="s">
+        <v>44</v>
       </c>
-      <c r="E14" s="5">
-        <v>1.0</v>
+      <c r="E14" s="4">
+        <v>1</v>
       </c>
-      <c r="F14" s="5">
-        <v>1500.0</v>
+      <c r="F14" s="4">
+        <v>50</v>
       </c>
       <c r="G14" s="4">
         <f>E14*F14</f>
-        <v>1500</v>
+        <v>50</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -978,18 +1099,17 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:25" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
       <c r="F15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="4">
-        <f>SUM(G14)</f>
-        <v>1500</v>
+        <f>SUM(G13+G14)</f>
+        <v>1550</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1010,7 +1130,7 @@
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1019,7 +1139,7 @@
       <c r="F16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>0.25</v>
       </c>
       <c r="H16" s="1"/>
@@ -1041,7 +1161,7 @@
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1052,7 +1172,7 @@
       </c>
       <c r="G17" s="4">
         <f>G15*(1+G16)</f>
-        <v>1875</v>
+        <v>1937.5</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1073,28 +1193,28 @@
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:25" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
+      <c r="C18" s="11" t="s">
+        <v>49</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>30</v>
+      <c r="E18" s="12" t="s">
+        <v>50</v>
       </c>
-      <c r="F18" s="5">
-        <v>3000.0</v>
+      <c r="F18" s="4">
+        <v>5000</v>
       </c>
       <c r="G18" s="4">
         <f>F18</f>
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1115,7 +1235,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1126,7 +1246,7 @@
       </c>
       <c r="G19" s="4">
         <f>G18-G17</f>
-        <v>1125</v>
+        <v>3062.5</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1147,7 +1267,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:25" ht="43" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>32</v>
       </c>
@@ -1188,25 +1308,25 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="6">
-        <v>2941.0</v>
+      <c r="C21" s="5">
+        <v>2941</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="5">
-        <v>1.0</v>
+      <c r="E21" s="4">
+        <v>1</v>
       </c>
-      <c r="F21" s="5">
-        <v>550.0</v>
+      <c r="F21" s="4">
+        <v>550</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" ref="G21:G23" si="2">E21*F21</f>
+        <f t="shared" ref="G21:G24" si="1">E21*F21</f>
         <v>550</v>
       </c>
       <c r="H21" s="1"/>
@@ -1228,25 +1348,25 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:25" ht="25" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="6">
-        <v>2941.0</v>
+      <c r="C22" s="5">
+        <v>2941</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="5">
-        <v>1.0</v>
+      <c r="E22" s="4">
+        <v>1</v>
       </c>
-      <c r="F22" s="5">
-        <v>550.0</v>
+      <c r="F22" s="4">
+        <v>550</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>550</v>
       </c>
       <c r="H22" s="1"/>
@@ -1268,26 +1388,25 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
-        <v>13</v>
+      <c r="B23" s="4" t="s">
+        <v>45</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>14</v>
+      <c r="C23" s="10" t="s">
+        <v>46</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>15</v>
+      <c r="D23" s="4" t="s">
+        <v>47</v>
       </c>
-      <c r="E23" s="5">
-        <v>1.0</v>
+      <c r="E23" s="4">
+        <v>1</v>
       </c>
-      <c r="F23" s="5">
-        <v>500.0</v>
+      <c r="F23" s="4">
+        <v>105</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="2"/>
-        <v>500</v>
+        <v>105</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -1308,18 +1427,26 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="2" t="s">
-        <v>23</v>
+      <c r="B24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>500</v>
       </c>
       <c r="G24" s="4">
-        <f>SUM(G21:G23)</f>
-        <v>1600</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -1340,17 +1467,18 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:25" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
-      <c r="G25" s="5">
-        <v>0.25</v>
+      <c r="G25" s="4">
+        <f>SUM(G21:G24)</f>
+        <v>1705</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -1371,18 +1499,17 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:25" ht="26" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26" s="4">
-        <f>G24*(1+G25)</f>
-        <v>2000</v>
+        <v>0.25</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -1403,28 +1530,18 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>1500.0</v>
+    <row r="27" spans="1:25" ht="13" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G27" s="4">
-        <f>F27*E27</f>
-        <v>1500</v>
+        <f>G25*(1+G26)</f>
+        <v>2131.25</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -1445,18 +1562,28 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="2" t="s">
-        <v>31</v>
+    <row r="28" spans="1:25" ht="13" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5000</v>
       </c>
       <c r="G28" s="4">
-        <f>G27-G26</f>
-        <v>-500</v>
+        <f>F28*E28</f>
+        <v>5000</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -1477,27 +1604,18 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
-        <v>36</v>
+    <row r="29" spans="1:25" ht="26" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="2" t="s">
+        <v>31</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>12</v>
+      <c r="G29" s="4">
+        <f>G28-G27</f>
+        <v>2868.75</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1518,28 +1636,27 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
+    <row r="30" spans="1:25" ht="39" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>34</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>39</v>
+      <c r="B30" s="3" t="s">
+        <v>7</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>28</v>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>29</v>
+      <c r="D30" s="3" t="s">
+        <v>9</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>30</v>
+      <c r="E30" s="3" t="s">
+        <v>35</v>
       </c>
-      <c r="F30" s="5">
-        <v>3000.0</v>
+      <c r="F30" s="3" t="s">
+        <v>11</v>
       </c>
-      <c r="G30" s="4">
-        <f>F30</f>
-        <v>3000</v>
+      <c r="G30" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1560,16 +1677,29 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="s">
-        <v>40</v>
+    <row r="31" spans="1:25" ht="25" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>36</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="4">
+        <v>5000</v>
+      </c>
+      <c r="G31" s="4">
+        <f>F31</f>
+        <v>5000</v>
+      </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -1589,8 +1719,10 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32">
-      <c r="A32" s="9"/>
+    <row r="32" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -1616,27 +1748,22 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33">
-      <c r="A33" s="9"/>
-      <c r="B33" s="7" t="s">
+    <row r="33" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>34</v>
+      <c r="C33" s="4" t="s">
+        <v>40</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>35</v>
+      <c r="D33" s="4" t="s">
+        <v>41</v>
       </c>
-      <c r="E33" s="5">
-        <v>1.0</v>
+      <c r="E33" s="6" t="s">
+        <v>48</v>
       </c>
-      <c r="F33" s="2">
-        <v>1500.0</v>
-      </c>
-      <c r="G33" s="4">
-        <f>F33*E33</f>
-        <v>1500</v>
-      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -1656,14 +1783,18 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34">
-      <c r="A34" s="10"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
+    <row r="34" spans="1:25" ht="13" x14ac:dyDescent="0.3">
+      <c r="A34" s="8"/>
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G34" s="4">
+        <f>F34*E34</f>
+        <v>5000</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -1683,19 +1814,14 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35">
-      <c r="A35" s="4"/>
+    <row r="35" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="4">
-        <f>G30-SUM(G31:G34)</f>
-        <v>1500</v>
-      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -1715,14 +1841,19 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+    <row r="36" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G36" s="4">
+        <f>G31-SUM(G32:G35)</f>
+        <v>0</v>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -1742,7 +1873,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1769,7 +1900,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1796,7 +1927,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1823,7 +1954,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1850,7 +1981,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1877,7 +2008,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1904,7 +2035,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1931,7 +2062,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1958,7 +2089,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1985,7 +2116,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2012,7 +2143,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2039,7 +2170,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2066,7 +2197,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2093,7 +2224,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2120,7 +2251,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2147,7 +2278,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2174,7 +2305,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2201,7 +2332,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2228,7 +2359,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2255,7 +2386,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2282,7 +2413,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2309,7 +2440,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2336,7 +2467,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2363,7 +2494,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2390,7 +2521,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2417,7 +2548,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2444,7 +2575,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2471,7 +2602,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2498,7 +2629,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2525,7 +2656,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2552,7 +2683,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2579,7 +2710,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2606,7 +2737,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2633,7 +2764,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2660,7 +2791,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -2687,7 +2818,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -2714,7 +2845,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -2741,7 +2872,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -2768,7 +2899,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -2795,7 +2926,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -2822,7 +2953,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -2849,7 +2980,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -2876,7 +3007,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -2903,7 +3034,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -2930,7 +3061,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2957,7 +3088,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -2984,7 +3115,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3011,7 +3142,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3038,7 +3169,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3065,7 +3196,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3092,7 +3223,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3119,7 +3250,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3146,7 +3277,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3173,7 +3304,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3200,7 +3331,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3227,7 +3358,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3254,7 +3385,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3281,7 +3412,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3308,7 +3439,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3335,7 +3466,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3362,7 +3493,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3389,7 +3520,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3416,7 +3547,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3443,7 +3574,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3470,7 +3601,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3497,7 +3628,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3524,7 +3655,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3551,7 +3682,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3578,7 +3709,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3605,7 +3736,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3632,7 +3763,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3659,7 +3790,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3686,7 +3817,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3713,7 +3844,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3740,7 +3871,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3767,7 +3898,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3794,7 +3925,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3821,7 +3952,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3848,7 +3979,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3875,7 +4006,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3902,7 +4033,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3929,7 +4060,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3956,7 +4087,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3983,7 +4114,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4010,7 +4141,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4037,7 +4168,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4064,7 +4195,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4091,7 +4222,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4118,7 +4249,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4145,7 +4276,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4172,7 +4303,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4199,7 +4330,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4226,7 +4357,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4253,7 +4384,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4280,7 +4411,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4307,7 +4438,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4334,7 +4465,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4361,7 +4492,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4388,7 +4519,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4415,7 +4546,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4442,7 +4573,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4469,7 +4600,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4496,7 +4627,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4523,7 +4654,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4550,7 +4681,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4577,7 +4708,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4604,7 +4735,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4631,7 +4762,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4658,7 +4789,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4685,7 +4816,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4712,7 +4843,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4739,7 +4870,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4766,7 +4897,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4793,7 +4924,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4820,7 +4951,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4847,7 +4978,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4874,7 +5005,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4901,7 +5032,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4928,7 +5059,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4955,7 +5086,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4982,7 +5113,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5009,7 +5140,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5036,7 +5167,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5063,7 +5194,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5090,7 +5221,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5117,7 +5248,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5144,7 +5275,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5171,7 +5302,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5198,7 +5329,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5225,7 +5356,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5252,7 +5383,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5279,7 +5410,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5306,7 +5437,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5333,7 +5464,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5360,7 +5491,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5387,7 +5518,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5414,7 +5545,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5441,7 +5572,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5468,7 +5599,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5495,7 +5626,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5522,7 +5653,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5549,7 +5680,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5576,7 +5707,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -5603,7 +5734,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -5630,7 +5761,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -5657,7 +5788,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -5684,7 +5815,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -5711,7 +5842,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -5738,7 +5869,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -5765,7 +5896,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -5792,7 +5923,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -5819,7 +5950,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -5846,7 +5977,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -5873,7 +6004,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -5900,7 +6031,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -5927,7 +6058,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -5954,7 +6085,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -5981,7 +6112,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6008,7 +6139,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6035,7 +6166,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6062,7 +6193,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6089,7 +6220,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6116,7 +6247,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6143,7 +6274,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6170,7 +6301,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6197,7 +6328,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6224,7 +6355,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6251,7 +6382,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6278,7 +6409,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6305,7 +6436,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6332,7 +6463,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6359,7 +6490,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6386,7 +6517,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6413,7 +6544,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6440,7 +6571,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6467,7 +6598,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6494,7 +6625,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6521,7 +6652,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -6548,7 +6679,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -6575,7 +6706,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -6602,7 +6733,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -6629,7 +6760,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -6656,7 +6787,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -6683,7 +6814,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -6710,7 +6841,7 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -6737,7 +6868,7 @@
       <c r="X221" s="1"/>
       <c r="Y221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -6764,7 +6895,7 @@
       <c r="X222" s="1"/>
       <c r="Y222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -6791,7 +6922,7 @@
       <c r="X223" s="1"/>
       <c r="Y223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -6818,7 +6949,7 @@
       <c r="X224" s="1"/>
       <c r="Y224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -6845,7 +6976,7 @@
       <c r="X225" s="1"/>
       <c r="Y225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -6872,7 +7003,7 @@
       <c r="X226" s="1"/>
       <c r="Y226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -6899,7 +7030,7 @@
       <c r="X227" s="1"/>
       <c r="Y227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -6926,7 +7057,7 @@
       <c r="X228" s="1"/>
       <c r="Y228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -6953,7 +7084,7 @@
       <c r="X229" s="1"/>
       <c r="Y229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -6980,7 +7111,7 @@
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -7007,7 +7138,7 @@
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -7034,7 +7165,7 @@
       <c r="X232" s="1"/>
       <c r="Y232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -7061,7 +7192,7 @@
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -7088,7 +7219,7 @@
       <c r="X234" s="1"/>
       <c r="Y234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -7115,7 +7246,7 @@
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -7142,7 +7273,7 @@
       <c r="X236" s="1"/>
       <c r="Y236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -7169,7 +7300,7 @@
       <c r="X237" s="1"/>
       <c r="Y237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -7196,7 +7327,7 @@
       <c r="X238" s="1"/>
       <c r="Y238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -7223,7 +7354,7 @@
       <c r="X239" s="1"/>
       <c r="Y239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -7250,7 +7381,7 @@
       <c r="X240" s="1"/>
       <c r="Y240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -7277,7 +7408,7 @@
       <c r="X241" s="1"/>
       <c r="Y241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -7304,7 +7435,7 @@
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -7331,7 +7462,7 @@
       <c r="X243" s="1"/>
       <c r="Y243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -7358,7 +7489,7 @@
       <c r="X244" s="1"/>
       <c r="Y244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -7385,7 +7516,7 @@
       <c r="X245" s="1"/>
       <c r="Y245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -7412,7 +7543,7 @@
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -7439,7 +7570,7 @@
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -7466,7 +7597,7 @@
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -7493,7 +7624,7 @@
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -7520,7 +7651,7 @@
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -7547,7 +7678,7 @@
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -7574,7 +7705,7 @@
       <c r="X252" s="1"/>
       <c r="Y252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -7601,7 +7732,7 @@
       <c r="X253" s="1"/>
       <c r="Y253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -7628,7 +7759,7 @@
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -7655,7 +7786,7 @@
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -7682,7 +7813,7 @@
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -7709,7 +7840,7 @@
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -7736,7 +7867,7 @@
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -7763,7 +7894,7 @@
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -7790,7 +7921,7 @@
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -7817,7 +7948,7 @@
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -7844,7 +7975,7 @@
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -7871,7 +8002,7 @@
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -7898,7 +8029,7 @@
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -7925,7 +8056,7 @@
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -7952,7 +8083,7 @@
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -7979,7 +8110,7 @@
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -8006,7 +8137,7 @@
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -8033,7 +8164,7 @@
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -8060,7 +8191,7 @@
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -8087,7 +8218,7 @@
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -8114,7 +8245,7 @@
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -8141,7 +8272,7 @@
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -8168,7 +8299,7 @@
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -8195,7 +8326,7 @@
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -8222,7 +8353,7 @@
       <c r="X276" s="1"/>
       <c r="Y276" s="1"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -8249,7 +8380,7 @@
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -8276,7 +8407,7 @@
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -8303,7 +8434,7 @@
       <c r="X279" s="1"/>
       <c r="Y279" s="1"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -8330,7 +8461,7 @@
       <c r="X280" s="1"/>
       <c r="Y280" s="1"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -8357,7 +8488,7 @@
       <c r="X281" s="1"/>
       <c r="Y281" s="1"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -8384,7 +8515,7 @@
       <c r="X282" s="1"/>
       <c r="Y282" s="1"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -8411,7 +8542,7 @@
       <c r="X283" s="1"/>
       <c r="Y283" s="1"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -8438,7 +8569,7 @@
       <c r="X284" s="1"/>
       <c r="Y284" s="1"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -8465,7 +8596,7 @@
       <c r="X285" s="1"/>
       <c r="Y285" s="1"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -8492,7 +8623,7 @@
       <c r="X286" s="1"/>
       <c r="Y286" s="1"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -8519,7 +8650,7 @@
       <c r="X287" s="1"/>
       <c r="Y287" s="1"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -8546,7 +8677,7 @@
       <c r="X288" s="1"/>
       <c r="Y288" s="1"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -8573,7 +8704,7 @@
       <c r="X289" s="1"/>
       <c r="Y289" s="1"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -8600,7 +8731,7 @@
       <c r="X290" s="1"/>
       <c r="Y290" s="1"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -8627,7 +8758,7 @@
       <c r="X291" s="1"/>
       <c r="Y291" s="1"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -8654,7 +8785,7 @@
       <c r="X292" s="1"/>
       <c r="Y292" s="1"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -8681,7 +8812,7 @@
       <c r="X293" s="1"/>
       <c r="Y293" s="1"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -8708,7 +8839,7 @@
       <c r="X294" s="1"/>
       <c r="Y294" s="1"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -8735,7 +8866,7 @@
       <c r="X295" s="1"/>
       <c r="Y295" s="1"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -8762,7 +8893,7 @@
       <c r="X296" s="1"/>
       <c r="Y296" s="1"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -8789,7 +8920,7 @@
       <c r="X297" s="1"/>
       <c r="Y297" s="1"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -8816,7 +8947,7 @@
       <c r="X298" s="1"/>
       <c r="Y298" s="1"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -8843,7 +8974,7 @@
       <c r="X299" s="1"/>
       <c r="Y299" s="1"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -8870,7 +9001,7 @@
       <c r="X300" s="1"/>
       <c r="Y300" s="1"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -8897,7 +9028,7 @@
       <c r="X301" s="1"/>
       <c r="Y301" s="1"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -8924,7 +9055,7 @@
       <c r="X302" s="1"/>
       <c r="Y302" s="1"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -8951,7 +9082,7 @@
       <c r="X303" s="1"/>
       <c r="Y303" s="1"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -8978,7 +9109,7 @@
       <c r="X304" s="1"/>
       <c r="Y304" s="1"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -9005,7 +9136,7 @@
       <c r="X305" s="1"/>
       <c r="Y305" s="1"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -9032,7 +9163,7 @@
       <c r="X306" s="1"/>
       <c r="Y306" s="1"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -9059,7 +9190,7 @@
       <c r="X307" s="1"/>
       <c r="Y307" s="1"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -9086,7 +9217,7 @@
       <c r="X308" s="1"/>
       <c r="Y308" s="1"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -9113,7 +9244,7 @@
       <c r="X309" s="1"/>
       <c r="Y309" s="1"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -9140,7 +9271,7 @@
       <c r="X310" s="1"/>
       <c r="Y310" s="1"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -9167,7 +9298,7 @@
       <c r="X311" s="1"/>
       <c r="Y311" s="1"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -9194,7 +9325,7 @@
       <c r="X312" s="1"/>
       <c r="Y312" s="1"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -9221,7 +9352,7 @@
       <c r="X313" s="1"/>
       <c r="Y313" s="1"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -9248,7 +9379,7 @@
       <c r="X314" s="1"/>
       <c r="Y314" s="1"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -9275,7 +9406,7 @@
       <c r="X315" s="1"/>
       <c r="Y315" s="1"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -9302,7 +9433,7 @@
       <c r="X316" s="1"/>
       <c r="Y316" s="1"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -9329,7 +9460,7 @@
       <c r="X317" s="1"/>
       <c r="Y317" s="1"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -9356,7 +9487,7 @@
       <c r="X318" s="1"/>
       <c r="Y318" s="1"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -9383,7 +9514,7 @@
       <c r="X319" s="1"/>
       <c r="Y319" s="1"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -9410,7 +9541,7 @@
       <c r="X320" s="1"/>
       <c r="Y320" s="1"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -9437,7 +9568,7 @@
       <c r="X321" s="1"/>
       <c r="Y321" s="1"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -9464,7 +9595,7 @@
       <c r="X322" s="1"/>
       <c r="Y322" s="1"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -9491,7 +9622,7 @@
       <c r="X323" s="1"/>
       <c r="Y323" s="1"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -9518,7 +9649,7 @@
       <c r="X324" s="1"/>
       <c r="Y324" s="1"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -9545,7 +9676,7 @@
       <c r="X325" s="1"/>
       <c r="Y325" s="1"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -9572,7 +9703,7 @@
       <c r="X326" s="1"/>
       <c r="Y326" s="1"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -9599,7 +9730,7 @@
       <c r="X327" s="1"/>
       <c r="Y327" s="1"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -9626,7 +9757,7 @@
       <c r="X328" s="1"/>
       <c r="Y328" s="1"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -9653,7 +9784,7 @@
       <c r="X329" s="1"/>
       <c r="Y329" s="1"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -9680,7 +9811,7 @@
       <c r="X330" s="1"/>
       <c r="Y330" s="1"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -9707,7 +9838,7 @@
       <c r="X331" s="1"/>
       <c r="Y331" s="1"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -9734,7 +9865,7 @@
       <c r="X332" s="1"/>
       <c r="Y332" s="1"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -9761,7 +9892,7 @@
       <c r="X333" s="1"/>
       <c r="Y333" s="1"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -9788,7 +9919,7 @@
       <c r="X334" s="1"/>
       <c r="Y334" s="1"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -9815,7 +9946,7 @@
       <c r="X335" s="1"/>
       <c r="Y335" s="1"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -9842,7 +9973,7 @@
       <c r="X336" s="1"/>
       <c r="Y336" s="1"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -9869,7 +10000,7 @@
       <c r="X337" s="1"/>
       <c r="Y337" s="1"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -9896,7 +10027,7 @@
       <c r="X338" s="1"/>
       <c r="Y338" s="1"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -9923,7 +10054,7 @@
       <c r="X339" s="1"/>
       <c r="Y339" s="1"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -9950,7 +10081,7 @@
       <c r="X340" s="1"/>
       <c r="Y340" s="1"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -9977,7 +10108,7 @@
       <c r="X341" s="1"/>
       <c r="Y341" s="1"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -10004,7 +10135,7 @@
       <c r="X342" s="1"/>
       <c r="Y342" s="1"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -10031,7 +10162,7 @@
       <c r="X343" s="1"/>
       <c r="Y343" s="1"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -10058,7 +10189,7 @@
       <c r="X344" s="1"/>
       <c r="Y344" s="1"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -10085,7 +10216,7 @@
       <c r="X345" s="1"/>
       <c r="Y345" s="1"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -10112,7 +10243,7 @@
       <c r="X346" s="1"/>
       <c r="Y346" s="1"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -10139,7 +10270,7 @@
       <c r="X347" s="1"/>
       <c r="Y347" s="1"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -10166,7 +10297,7 @@
       <c r="X348" s="1"/>
       <c r="Y348" s="1"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -10193,7 +10324,7 @@
       <c r="X349" s="1"/>
       <c r="Y349" s="1"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -10220,7 +10351,7 @@
       <c r="X350" s="1"/>
       <c r="Y350" s="1"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -10247,7 +10378,7 @@
       <c r="X351" s="1"/>
       <c r="Y351" s="1"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -10274,7 +10405,7 @@
       <c r="X352" s="1"/>
       <c r="Y352" s="1"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -10301,7 +10432,7 @@
       <c r="X353" s="1"/>
       <c r="Y353" s="1"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -10328,7 +10459,7 @@
       <c r="X354" s="1"/>
       <c r="Y354" s="1"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -10355,7 +10486,7 @@
       <c r="X355" s="1"/>
       <c r="Y355" s="1"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -10382,7 +10513,7 @@
       <c r="X356" s="1"/>
       <c r="Y356" s="1"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -10409,7 +10540,7 @@
       <c r="X357" s="1"/>
       <c r="Y357" s="1"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -10436,7 +10567,7 @@
       <c r="X358" s="1"/>
       <c r="Y358" s="1"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -10463,7 +10594,7 @@
       <c r="X359" s="1"/>
       <c r="Y359" s="1"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -10490,7 +10621,7 @@
       <c r="X360" s="1"/>
       <c r="Y360" s="1"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -10517,7 +10648,7 @@
       <c r="X361" s="1"/>
       <c r="Y361" s="1"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -10544,7 +10675,7 @@
       <c r="X362" s="1"/>
       <c r="Y362" s="1"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -10571,7 +10702,7 @@
       <c r="X363" s="1"/>
       <c r="Y363" s="1"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -10598,7 +10729,7 @@
       <c r="X364" s="1"/>
       <c r="Y364" s="1"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -10625,7 +10756,7 @@
       <c r="X365" s="1"/>
       <c r="Y365" s="1"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -10652,7 +10783,7 @@
       <c r="X366" s="1"/>
       <c r="Y366" s="1"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -10679,7 +10810,7 @@
       <c r="X367" s="1"/>
       <c r="Y367" s="1"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -10706,7 +10837,7 @@
       <c r="X368" s="1"/>
       <c r="Y368" s="1"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -10733,7 +10864,7 @@
       <c r="X369" s="1"/>
       <c r="Y369" s="1"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -10760,7 +10891,7 @@
       <c r="X370" s="1"/>
       <c r="Y370" s="1"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -10787,7 +10918,7 @@
       <c r="X371" s="1"/>
       <c r="Y371" s="1"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -10814,7 +10945,7 @@
       <c r="X372" s="1"/>
       <c r="Y372" s="1"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -10841,7 +10972,7 @@
       <c r="X373" s="1"/>
       <c r="Y373" s="1"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -10868,7 +10999,7 @@
       <c r="X374" s="1"/>
       <c r="Y374" s="1"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -10895,7 +11026,7 @@
       <c r="X375" s="1"/>
       <c r="Y375" s="1"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -10922,7 +11053,7 @@
       <c r="X376" s="1"/>
       <c r="Y376" s="1"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -10949,7 +11080,7 @@
       <c r="X377" s="1"/>
       <c r="Y377" s="1"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -10976,7 +11107,7 @@
       <c r="X378" s="1"/>
       <c r="Y378" s="1"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -11003,7 +11134,7 @@
       <c r="X379" s="1"/>
       <c r="Y379" s="1"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -11030,7 +11161,7 @@
       <c r="X380" s="1"/>
       <c r="Y380" s="1"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -11057,7 +11188,7 @@
       <c r="X381" s="1"/>
       <c r="Y381" s="1"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -11084,7 +11215,7 @@
       <c r="X382" s="1"/>
       <c r="Y382" s="1"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -11111,7 +11242,7 @@
       <c r="X383" s="1"/>
       <c r="Y383" s="1"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -11138,7 +11269,7 @@
       <c r="X384" s="1"/>
       <c r="Y384" s="1"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -11165,7 +11296,7 @@
       <c r="X385" s="1"/>
       <c r="Y385" s="1"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -11192,7 +11323,7 @@
       <c r="X386" s="1"/>
       <c r="Y386" s="1"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -11219,7 +11350,7 @@
       <c r="X387" s="1"/>
       <c r="Y387" s="1"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -11246,7 +11377,7 @@
       <c r="X388" s="1"/>
       <c r="Y388" s="1"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -11273,7 +11404,7 @@
       <c r="X389" s="1"/>
       <c r="Y389" s="1"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -11300,7 +11431,7 @@
       <c r="X390" s="1"/>
       <c r="Y390" s="1"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -11327,7 +11458,7 @@
       <c r="X391" s="1"/>
       <c r="Y391" s="1"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -11354,7 +11485,7 @@
       <c r="X392" s="1"/>
       <c r="Y392" s="1"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -11381,7 +11512,7 @@
       <c r="X393" s="1"/>
       <c r="Y393" s="1"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -11408,7 +11539,7 @@
       <c r="X394" s="1"/>
       <c r="Y394" s="1"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -11435,7 +11566,7 @@
       <c r="X395" s="1"/>
       <c r="Y395" s="1"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -11462,7 +11593,7 @@
       <c r="X396" s="1"/>
       <c r="Y396" s="1"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -11489,7 +11620,7 @@
       <c r="X397" s="1"/>
       <c r="Y397" s="1"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -11516,7 +11647,7 @@
       <c r="X398" s="1"/>
       <c r="Y398" s="1"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -11543,7 +11674,7 @@
       <c r="X399" s="1"/>
       <c r="Y399" s="1"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -11570,7 +11701,7 @@
       <c r="X400" s="1"/>
       <c r="Y400" s="1"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -11597,7 +11728,7 @@
       <c r="X401" s="1"/>
       <c r="Y401" s="1"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -11624,7 +11755,7 @@
       <c r="X402" s="1"/>
       <c r="Y402" s="1"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -11651,7 +11782,7 @@
       <c r="X403" s="1"/>
       <c r="Y403" s="1"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -11678,7 +11809,7 @@
       <c r="X404" s="1"/>
       <c r="Y404" s="1"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -11705,7 +11836,7 @@
       <c r="X405" s="1"/>
       <c r="Y405" s="1"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -11732,7 +11863,7 @@
       <c r="X406" s="1"/>
       <c r="Y406" s="1"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -11759,7 +11890,7 @@
       <c r="X407" s="1"/>
       <c r="Y407" s="1"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -11786,7 +11917,7 @@
       <c r="X408" s="1"/>
       <c r="Y408" s="1"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -11813,7 +11944,7 @@
       <c r="X409" s="1"/>
       <c r="Y409" s="1"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -11840,7 +11971,7 @@
       <c r="X410" s="1"/>
       <c r="Y410" s="1"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -11867,7 +11998,7 @@
       <c r="X411" s="1"/>
       <c r="Y411" s="1"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -11894,7 +12025,7 @@
       <c r="X412" s="1"/>
       <c r="Y412" s="1"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -11921,7 +12052,7 @@
       <c r="X413" s="1"/>
       <c r="Y413" s="1"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -11948,7 +12079,7 @@
       <c r="X414" s="1"/>
       <c r="Y414" s="1"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -11975,7 +12106,7 @@
       <c r="X415" s="1"/>
       <c r="Y415" s="1"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -12002,7 +12133,7 @@
       <c r="X416" s="1"/>
       <c r="Y416" s="1"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -12029,7 +12160,7 @@
       <c r="X417" s="1"/>
       <c r="Y417" s="1"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -12056,7 +12187,7 @@
       <c r="X418" s="1"/>
       <c r="Y418" s="1"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -12083,7 +12214,7 @@
       <c r="X419" s="1"/>
       <c r="Y419" s="1"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -12110,7 +12241,7 @@
       <c r="X420" s="1"/>
       <c r="Y420" s="1"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -12137,7 +12268,7 @@
       <c r="X421" s="1"/>
       <c r="Y421" s="1"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -12164,7 +12295,7 @@
       <c r="X422" s="1"/>
       <c r="Y422" s="1"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -12191,7 +12322,7 @@
       <c r="X423" s="1"/>
       <c r="Y423" s="1"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -12218,7 +12349,7 @@
       <c r="X424" s="1"/>
       <c r="Y424" s="1"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -12245,7 +12376,7 @@
       <c r="X425" s="1"/>
       <c r="Y425" s="1"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -12272,7 +12403,7 @@
       <c r="X426" s="1"/>
       <c r="Y426" s="1"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -12299,7 +12430,7 @@
       <c r="X427" s="1"/>
       <c r="Y427" s="1"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -12326,7 +12457,7 @@
       <c r="X428" s="1"/>
       <c r="Y428" s="1"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -12353,7 +12484,7 @@
       <c r="X429" s="1"/>
       <c r="Y429" s="1"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -12380,7 +12511,7 @@
       <c r="X430" s="1"/>
       <c r="Y430" s="1"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -12407,7 +12538,7 @@
       <c r="X431" s="1"/>
       <c r="Y431" s="1"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -12434,7 +12565,7 @@
       <c r="X432" s="1"/>
       <c r="Y432" s="1"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -12461,7 +12592,7 @@
       <c r="X433" s="1"/>
       <c r="Y433" s="1"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -12488,7 +12619,7 @@
       <c r="X434" s="1"/>
       <c r="Y434" s="1"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -12515,7 +12646,7 @@
       <c r="X435" s="1"/>
       <c r="Y435" s="1"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -12542,7 +12673,7 @@
       <c r="X436" s="1"/>
       <c r="Y436" s="1"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -12569,7 +12700,7 @@
       <c r="X437" s="1"/>
       <c r="Y437" s="1"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -12596,7 +12727,7 @@
       <c r="X438" s="1"/>
       <c r="Y438" s="1"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -12623,7 +12754,7 @@
       <c r="X439" s="1"/>
       <c r="Y439" s="1"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -12650,7 +12781,7 @@
       <c r="X440" s="1"/>
       <c r="Y440" s="1"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -12677,7 +12808,7 @@
       <c r="X441" s="1"/>
       <c r="Y441" s="1"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -12704,7 +12835,7 @@
       <c r="X442" s="1"/>
       <c r="Y442" s="1"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -12731,7 +12862,7 @@
       <c r="X443" s="1"/>
       <c r="Y443" s="1"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -12758,7 +12889,7 @@
       <c r="X444" s="1"/>
       <c r="Y444" s="1"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -12785,7 +12916,7 @@
       <c r="X445" s="1"/>
       <c r="Y445" s="1"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -12812,7 +12943,7 @@
       <c r="X446" s="1"/>
       <c r="Y446" s="1"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -12839,7 +12970,7 @@
       <c r="X447" s="1"/>
       <c r="Y447" s="1"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -12866,7 +12997,7 @@
       <c r="X448" s="1"/>
       <c r="Y448" s="1"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -12893,7 +13024,7 @@
       <c r="X449" s="1"/>
       <c r="Y449" s="1"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -12920,7 +13051,7 @@
       <c r="X450" s="1"/>
       <c r="Y450" s="1"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -12947,7 +13078,7 @@
       <c r="X451" s="1"/>
       <c r="Y451" s="1"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -12974,7 +13105,7 @@
       <c r="X452" s="1"/>
       <c r="Y452" s="1"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -13001,7 +13132,7 @@
       <c r="X453" s="1"/>
       <c r="Y453" s="1"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -13028,7 +13159,7 @@
       <c r="X454" s="1"/>
       <c r="Y454" s="1"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -13055,7 +13186,7 @@
       <c r="X455" s="1"/>
       <c r="Y455" s="1"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -13082,7 +13213,7 @@
       <c r="X456" s="1"/>
       <c r="Y456" s="1"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -13109,7 +13240,7 @@
       <c r="X457" s="1"/>
       <c r="Y457" s="1"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -13136,7 +13267,7 @@
       <c r="X458" s="1"/>
       <c r="Y458" s="1"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -13163,7 +13294,7 @@
       <c r="X459" s="1"/>
       <c r="Y459" s="1"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -13190,7 +13321,7 @@
       <c r="X460" s="1"/>
       <c r="Y460" s="1"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -13217,7 +13348,7 @@
       <c r="X461" s="1"/>
       <c r="Y461" s="1"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -13244,7 +13375,7 @@
       <c r="X462" s="1"/>
       <c r="Y462" s="1"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -13271,7 +13402,7 @@
       <c r="X463" s="1"/>
       <c r="Y463" s="1"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -13298,7 +13429,7 @@
       <c r="X464" s="1"/>
       <c r="Y464" s="1"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -13325,7 +13456,7 @@
       <c r="X465" s="1"/>
       <c r="Y465" s="1"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -13352,7 +13483,7 @@
       <c r="X466" s="1"/>
       <c r="Y466" s="1"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -13379,7 +13510,7 @@
       <c r="X467" s="1"/>
       <c r="Y467" s="1"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -13406,7 +13537,7 @@
       <c r="X468" s="1"/>
       <c r="Y468" s="1"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -13433,7 +13564,7 @@
       <c r="X469" s="1"/>
       <c r="Y469" s="1"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -13460,7 +13591,7 @@
       <c r="X470" s="1"/>
       <c r="Y470" s="1"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -13487,7 +13618,7 @@
       <c r="X471" s="1"/>
       <c r="Y471" s="1"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -13514,7 +13645,7 @@
       <c r="X472" s="1"/>
       <c r="Y472" s="1"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -13541,7 +13672,7 @@
       <c r="X473" s="1"/>
       <c r="Y473" s="1"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -13568,7 +13699,7 @@
       <c r="X474" s="1"/>
       <c r="Y474" s="1"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -13595,7 +13726,7 @@
       <c r="X475" s="1"/>
       <c r="Y475" s="1"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -13622,7 +13753,7 @@
       <c r="X476" s="1"/>
       <c r="Y476" s="1"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -13649,7 +13780,7 @@
       <c r="X477" s="1"/>
       <c r="Y477" s="1"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -13676,7 +13807,7 @@
       <c r="X478" s="1"/>
       <c r="Y478" s="1"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -13703,7 +13834,7 @@
       <c r="X479" s="1"/>
       <c r="Y479" s="1"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -13730,7 +13861,7 @@
       <c r="X480" s="1"/>
       <c r="Y480" s="1"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -13757,7 +13888,7 @@
       <c r="X481" s="1"/>
       <c r="Y481" s="1"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -13784,7 +13915,7 @@
       <c r="X482" s="1"/>
       <c r="Y482" s="1"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -13811,7 +13942,7 @@
       <c r="X483" s="1"/>
       <c r="Y483" s="1"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -13838,7 +13969,7 @@
       <c r="X484" s="1"/>
       <c r="Y484" s="1"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -13865,7 +13996,7 @@
       <c r="X485" s="1"/>
       <c r="Y485" s="1"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -13892,7 +14023,7 @@
       <c r="X486" s="1"/>
       <c r="Y486" s="1"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -13919,7 +14050,7 @@
       <c r="X487" s="1"/>
       <c r="Y487" s="1"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -13946,7 +14077,7 @@
       <c r="X488" s="1"/>
       <c r="Y488" s="1"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -13973,7 +14104,7 @@
       <c r="X489" s="1"/>
       <c r="Y489" s="1"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -14000,7 +14131,7 @@
       <c r="X490" s="1"/>
       <c r="Y490" s="1"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -14027,7 +14158,7 @@
       <c r="X491" s="1"/>
       <c r="Y491" s="1"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -14054,7 +14185,7 @@
       <c r="X492" s="1"/>
       <c r="Y492" s="1"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -14081,7 +14212,7 @@
       <c r="X493" s="1"/>
       <c r="Y493" s="1"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -14108,7 +14239,7 @@
       <c r="X494" s="1"/>
       <c r="Y494" s="1"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -14135,7 +14266,7 @@
       <c r="X495" s="1"/>
       <c r="Y495" s="1"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -14162,7 +14293,7 @@
       <c r="X496" s="1"/>
       <c r="Y496" s="1"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -14189,7 +14320,7 @@
       <c r="X497" s="1"/>
       <c r="Y497" s="1"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -14216,7 +14347,7 @@
       <c r="X498" s="1"/>
       <c r="Y498" s="1"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -14243,7 +14374,7 @@
       <c r="X499" s="1"/>
       <c r="Y499" s="1"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -14270,7 +14401,7 @@
       <c r="X500" s="1"/>
       <c r="Y500" s="1"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -14297,7 +14428,7 @@
       <c r="X501" s="1"/>
       <c r="Y501" s="1"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -14324,7 +14455,7 @@
       <c r="X502" s="1"/>
       <c r="Y502" s="1"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -14351,7 +14482,7 @@
       <c r="X503" s="1"/>
       <c r="Y503" s="1"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -14378,7 +14509,7 @@
       <c r="X504" s="1"/>
       <c r="Y504" s="1"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -14405,7 +14536,7 @@
       <c r="X505" s="1"/>
       <c r="Y505" s="1"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -14432,7 +14563,7 @@
       <c r="X506" s="1"/>
       <c r="Y506" s="1"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -14459,7 +14590,7 @@
       <c r="X507" s="1"/>
       <c r="Y507" s="1"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -14486,7 +14617,7 @@
       <c r="X508" s="1"/>
       <c r="Y508" s="1"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -14513,7 +14644,7 @@
       <c r="X509" s="1"/>
       <c r="Y509" s="1"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -14540,7 +14671,7 @@
       <c r="X510" s="1"/>
       <c r="Y510" s="1"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -14567,7 +14698,7 @@
       <c r="X511" s="1"/>
       <c r="Y511" s="1"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -14594,7 +14725,7 @@
       <c r="X512" s="1"/>
       <c r="Y512" s="1"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -14621,7 +14752,7 @@
       <c r="X513" s="1"/>
       <c r="Y513" s="1"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -14648,7 +14779,7 @@
       <c r="X514" s="1"/>
       <c r="Y514" s="1"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -14675,7 +14806,7 @@
       <c r="X515" s="1"/>
       <c r="Y515" s="1"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -14702,7 +14833,7 @@
       <c r="X516" s="1"/>
       <c r="Y516" s="1"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -14729,7 +14860,7 @@
       <c r="X517" s="1"/>
       <c r="Y517" s="1"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -14756,7 +14887,7 @@
       <c r="X518" s="1"/>
       <c r="Y518" s="1"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -14783,7 +14914,7 @@
       <c r="X519" s="1"/>
       <c r="Y519" s="1"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -14810,7 +14941,7 @@
       <c r="X520" s="1"/>
       <c r="Y520" s="1"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -14837,7 +14968,7 @@
       <c r="X521" s="1"/>
       <c r="Y521" s="1"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -14864,7 +14995,7 @@
       <c r="X522" s="1"/>
       <c r="Y522" s="1"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -14891,7 +15022,7 @@
       <c r="X523" s="1"/>
       <c r="Y523" s="1"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -14918,7 +15049,7 @@
       <c r="X524" s="1"/>
       <c r="Y524" s="1"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -14945,7 +15076,7 @@
       <c r="X525" s="1"/>
       <c r="Y525" s="1"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -14972,7 +15103,7 @@
       <c r="X526" s="1"/>
       <c r="Y526" s="1"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -14999,7 +15130,7 @@
       <c r="X527" s="1"/>
       <c r="Y527" s="1"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -15026,7 +15157,7 @@
       <c r="X528" s="1"/>
       <c r="Y528" s="1"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -15053,7 +15184,7 @@
       <c r="X529" s="1"/>
       <c r="Y529" s="1"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -15080,7 +15211,7 @@
       <c r="X530" s="1"/>
       <c r="Y530" s="1"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -15107,7 +15238,7 @@
       <c r="X531" s="1"/>
       <c r="Y531" s="1"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -15134,7 +15265,7 @@
       <c r="X532" s="1"/>
       <c r="Y532" s="1"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -15161,7 +15292,7 @@
       <c r="X533" s="1"/>
       <c r="Y533" s="1"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -15188,7 +15319,7 @@
       <c r="X534" s="1"/>
       <c r="Y534" s="1"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -15215,7 +15346,7 @@
       <c r="X535" s="1"/>
       <c r="Y535" s="1"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -15242,7 +15373,7 @@
       <c r="X536" s="1"/>
       <c r="Y536" s="1"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -15269,7 +15400,7 @@
       <c r="X537" s="1"/>
       <c r="Y537" s="1"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -15296,7 +15427,7 @@
       <c r="X538" s="1"/>
       <c r="Y538" s="1"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -15323,7 +15454,7 @@
       <c r="X539" s="1"/>
       <c r="Y539" s="1"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -15350,7 +15481,7 @@
       <c r="X540" s="1"/>
       <c r="Y540" s="1"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -15377,7 +15508,7 @@
       <c r="X541" s="1"/>
       <c r="Y541" s="1"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -15404,7 +15535,7 @@
       <c r="X542" s="1"/>
       <c r="Y542" s="1"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -15431,7 +15562,7 @@
       <c r="X543" s="1"/>
       <c r="Y543" s="1"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -15458,7 +15589,7 @@
       <c r="X544" s="1"/>
       <c r="Y544" s="1"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -15485,7 +15616,7 @@
       <c r="X545" s="1"/>
       <c r="Y545" s="1"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -15512,7 +15643,7 @@
       <c r="X546" s="1"/>
       <c r="Y546" s="1"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -15539,7 +15670,7 @@
       <c r="X547" s="1"/>
       <c r="Y547" s="1"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -15566,7 +15697,7 @@
       <c r="X548" s="1"/>
       <c r="Y548" s="1"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -15593,7 +15724,7 @@
       <c r="X549" s="1"/>
       <c r="Y549" s="1"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -15620,7 +15751,7 @@
       <c r="X550" s="1"/>
       <c r="Y550" s="1"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -15647,7 +15778,7 @@
       <c r="X551" s="1"/>
       <c r="Y551" s="1"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -15674,7 +15805,7 @@
       <c r="X552" s="1"/>
       <c r="Y552" s="1"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -15701,7 +15832,7 @@
       <c r="X553" s="1"/>
       <c r="Y553" s="1"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -15728,7 +15859,7 @@
       <c r="X554" s="1"/>
       <c r="Y554" s="1"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -15755,7 +15886,7 @@
       <c r="X555" s="1"/>
       <c r="Y555" s="1"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -15782,7 +15913,7 @@
       <c r="X556" s="1"/>
       <c r="Y556" s="1"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -15809,7 +15940,7 @@
       <c r="X557" s="1"/>
       <c r="Y557" s="1"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -15836,7 +15967,7 @@
       <c r="X558" s="1"/>
       <c r="Y558" s="1"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -15863,7 +15994,7 @@
       <c r="X559" s="1"/>
       <c r="Y559" s="1"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -15890,7 +16021,7 @@
       <c r="X560" s="1"/>
       <c r="Y560" s="1"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -15917,7 +16048,7 @@
       <c r="X561" s="1"/>
       <c r="Y561" s="1"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -15944,7 +16075,7 @@
       <c r="X562" s="1"/>
       <c r="Y562" s="1"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -15971,7 +16102,7 @@
       <c r="X563" s="1"/>
       <c r="Y563" s="1"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -15998,7 +16129,7 @@
       <c r="X564" s="1"/>
       <c r="Y564" s="1"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -16025,7 +16156,7 @@
       <c r="X565" s="1"/>
       <c r="Y565" s="1"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -16052,7 +16183,7 @@
       <c r="X566" s="1"/>
       <c r="Y566" s="1"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -16079,7 +16210,7 @@
       <c r="X567" s="1"/>
       <c r="Y567" s="1"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -16106,7 +16237,7 @@
       <c r="X568" s="1"/>
       <c r="Y568" s="1"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -16133,7 +16264,7 @@
       <c r="X569" s="1"/>
       <c r="Y569" s="1"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -16160,7 +16291,7 @@
       <c r="X570" s="1"/>
       <c r="Y570" s="1"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -16187,7 +16318,7 @@
       <c r="X571" s="1"/>
       <c r="Y571" s="1"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -16214,7 +16345,7 @@
       <c r="X572" s="1"/>
       <c r="Y572" s="1"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -16241,7 +16372,7 @@
       <c r="X573" s="1"/>
       <c r="Y573" s="1"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -16268,7 +16399,7 @@
       <c r="X574" s="1"/>
       <c r="Y574" s="1"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -16295,7 +16426,7 @@
       <c r="X575" s="1"/>
       <c r="Y575" s="1"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -16322,7 +16453,7 @@
       <c r="X576" s="1"/>
       <c r="Y576" s="1"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -16349,7 +16480,7 @@
       <c r="X577" s="1"/>
       <c r="Y577" s="1"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -16376,7 +16507,7 @@
       <c r="X578" s="1"/>
       <c r="Y578" s="1"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -16403,7 +16534,7 @@
       <c r="X579" s="1"/>
       <c r="Y579" s="1"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -16430,7 +16561,7 @@
       <c r="X580" s="1"/>
       <c r="Y580" s="1"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -16457,7 +16588,7 @@
       <c r="X581" s="1"/>
       <c r="Y581" s="1"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -16484,7 +16615,7 @@
       <c r="X582" s="1"/>
       <c r="Y582" s="1"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -16511,7 +16642,7 @@
       <c r="X583" s="1"/>
       <c r="Y583" s="1"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -16538,7 +16669,7 @@
       <c r="X584" s="1"/>
       <c r="Y584" s="1"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -16565,7 +16696,7 @@
       <c r="X585" s="1"/>
       <c r="Y585" s="1"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -16592,7 +16723,7 @@
       <c r="X586" s="1"/>
       <c r="Y586" s="1"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -16619,7 +16750,7 @@
       <c r="X587" s="1"/>
       <c r="Y587" s="1"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -16646,7 +16777,7 @@
       <c r="X588" s="1"/>
       <c r="Y588" s="1"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -16673,7 +16804,7 @@
       <c r="X589" s="1"/>
       <c r="Y589" s="1"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -16700,7 +16831,7 @@
       <c r="X590" s="1"/>
       <c r="Y590" s="1"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -16727,7 +16858,7 @@
       <c r="X591" s="1"/>
       <c r="Y591" s="1"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -16754,7 +16885,7 @@
       <c r="X592" s="1"/>
       <c r="Y592" s="1"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -16781,7 +16912,7 @@
       <c r="X593" s="1"/>
       <c r="Y593" s="1"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -16808,7 +16939,7 @@
       <c r="X594" s="1"/>
       <c r="Y594" s="1"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -16835,7 +16966,7 @@
       <c r="X595" s="1"/>
       <c r="Y595" s="1"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -16862,7 +16993,7 @@
       <c r="X596" s="1"/>
       <c r="Y596" s="1"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -16889,7 +17020,7 @@
       <c r="X597" s="1"/>
       <c r="Y597" s="1"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -16916,7 +17047,7 @@
       <c r="X598" s="1"/>
       <c r="Y598" s="1"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -16943,7 +17074,7 @@
       <c r="X599" s="1"/>
       <c r="Y599" s="1"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -16970,7 +17101,7 @@
       <c r="X600" s="1"/>
       <c r="Y600" s="1"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -16997,7 +17128,7 @@
       <c r="X601" s="1"/>
       <c r="Y601" s="1"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -17024,7 +17155,7 @@
       <c r="X602" s="1"/>
       <c r="Y602" s="1"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -17051,7 +17182,7 @@
       <c r="X603" s="1"/>
       <c r="Y603" s="1"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -17078,7 +17209,7 @@
       <c r="X604" s="1"/>
       <c r="Y604" s="1"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -17105,7 +17236,7 @@
       <c r="X605" s="1"/>
       <c r="Y605" s="1"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -17132,7 +17263,7 @@
       <c r="X606" s="1"/>
       <c r="Y606" s="1"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -17159,7 +17290,7 @@
       <c r="X607" s="1"/>
       <c r="Y607" s="1"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -17186,7 +17317,7 @@
       <c r="X608" s="1"/>
       <c r="Y608" s="1"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -17213,7 +17344,7 @@
       <c r="X609" s="1"/>
       <c r="Y609" s="1"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -17240,7 +17371,7 @@
       <c r="X610" s="1"/>
       <c r="Y610" s="1"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -17267,7 +17398,7 @@
       <c r="X611" s="1"/>
       <c r="Y611" s="1"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -17294,7 +17425,7 @@
       <c r="X612" s="1"/>
       <c r="Y612" s="1"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -17321,7 +17452,7 @@
       <c r="X613" s="1"/>
       <c r="Y613" s="1"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -17348,7 +17479,7 @@
       <c r="X614" s="1"/>
       <c r="Y614" s="1"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -17375,7 +17506,7 @@
       <c r="X615" s="1"/>
       <c r="Y615" s="1"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -17402,7 +17533,7 @@
       <c r="X616" s="1"/>
       <c r="Y616" s="1"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -17429,7 +17560,7 @@
       <c r="X617" s="1"/>
       <c r="Y617" s="1"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -17456,7 +17587,7 @@
       <c r="X618" s="1"/>
       <c r="Y618" s="1"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -17483,7 +17614,7 @@
       <c r="X619" s="1"/>
       <c r="Y619" s="1"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -17510,7 +17641,7 @@
       <c r="X620" s="1"/>
       <c r="Y620" s="1"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -17537,7 +17668,7 @@
       <c r="X621" s="1"/>
       <c r="Y621" s="1"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -17564,7 +17695,7 @@
       <c r="X622" s="1"/>
       <c r="Y622" s="1"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -17591,7 +17722,7 @@
       <c r="X623" s="1"/>
       <c r="Y623" s="1"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -17618,7 +17749,7 @@
       <c r="X624" s="1"/>
       <c r="Y624" s="1"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -17645,7 +17776,7 @@
       <c r="X625" s="1"/>
       <c r="Y625" s="1"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -17672,7 +17803,7 @@
       <c r="X626" s="1"/>
       <c r="Y626" s="1"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -17699,7 +17830,7 @@
       <c r="X627" s="1"/>
       <c r="Y627" s="1"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -17726,7 +17857,7 @@
       <c r="X628" s="1"/>
       <c r="Y628" s="1"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -17753,7 +17884,7 @@
       <c r="X629" s="1"/>
       <c r="Y629" s="1"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -17780,7 +17911,7 @@
       <c r="X630" s="1"/>
       <c r="Y630" s="1"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -17807,7 +17938,7 @@
       <c r="X631" s="1"/>
       <c r="Y631" s="1"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -17834,7 +17965,7 @@
       <c r="X632" s="1"/>
       <c r="Y632" s="1"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -17861,7 +17992,7 @@
       <c r="X633" s="1"/>
       <c r="Y633" s="1"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -17888,7 +18019,7 @@
       <c r="X634" s="1"/>
       <c r="Y634" s="1"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -17915,7 +18046,7 @@
       <c r="X635" s="1"/>
       <c r="Y635" s="1"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -17942,7 +18073,7 @@
       <c r="X636" s="1"/>
       <c r="Y636" s="1"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -17969,7 +18100,7 @@
       <c r="X637" s="1"/>
       <c r="Y637" s="1"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -17996,7 +18127,7 @@
       <c r="X638" s="1"/>
       <c r="Y638" s="1"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -18023,7 +18154,7 @@
       <c r="X639" s="1"/>
       <c r="Y639" s="1"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -18050,7 +18181,7 @@
       <c r="X640" s="1"/>
       <c r="Y640" s="1"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -18077,7 +18208,7 @@
       <c r="X641" s="1"/>
       <c r="Y641" s="1"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -18104,7 +18235,7 @@
       <c r="X642" s="1"/>
       <c r="Y642" s="1"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -18131,7 +18262,7 @@
       <c r="X643" s="1"/>
       <c r="Y643" s="1"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -18158,7 +18289,7 @@
       <c r="X644" s="1"/>
       <c r="Y644" s="1"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -18185,7 +18316,7 @@
       <c r="X645" s="1"/>
       <c r="Y645" s="1"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -18212,7 +18343,7 @@
       <c r="X646" s="1"/>
       <c r="Y646" s="1"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -18239,7 +18370,7 @@
       <c r="X647" s="1"/>
       <c r="Y647" s="1"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -18266,7 +18397,7 @@
       <c r="X648" s="1"/>
       <c r="Y648" s="1"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -18293,7 +18424,7 @@
       <c r="X649" s="1"/>
       <c r="Y649" s="1"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -18320,7 +18451,7 @@
       <c r="X650" s="1"/>
       <c r="Y650" s="1"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -18347,7 +18478,7 @@
       <c r="X651" s="1"/>
       <c r="Y651" s="1"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -18374,7 +18505,7 @@
       <c r="X652" s="1"/>
       <c r="Y652" s="1"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -18401,7 +18532,7 @@
       <c r="X653" s="1"/>
       <c r="Y653" s="1"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -18428,7 +18559,7 @@
       <c r="X654" s="1"/>
       <c r="Y654" s="1"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -18455,7 +18586,7 @@
       <c r="X655" s="1"/>
       <c r="Y655" s="1"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -18482,7 +18613,7 @@
       <c r="X656" s="1"/>
       <c r="Y656" s="1"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -18509,7 +18640,7 @@
       <c r="X657" s="1"/>
       <c r="Y657" s="1"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -18536,7 +18667,7 @@
       <c r="X658" s="1"/>
       <c r="Y658" s="1"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -18563,7 +18694,7 @@
       <c r="X659" s="1"/>
       <c r="Y659" s="1"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -18590,7 +18721,7 @@
       <c r="X660" s="1"/>
       <c r="Y660" s="1"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -18617,7 +18748,7 @@
       <c r="X661" s="1"/>
       <c r="Y661" s="1"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -18644,7 +18775,7 @@
       <c r="X662" s="1"/>
       <c r="Y662" s="1"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -18671,7 +18802,7 @@
       <c r="X663" s="1"/>
       <c r="Y663" s="1"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -18698,7 +18829,7 @@
       <c r="X664" s="1"/>
       <c r="Y664" s="1"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -18725,7 +18856,7 @@
       <c r="X665" s="1"/>
       <c r="Y665" s="1"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -18752,7 +18883,7 @@
       <c r="X666" s="1"/>
       <c r="Y666" s="1"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -18779,7 +18910,7 @@
       <c r="X667" s="1"/>
       <c r="Y667" s="1"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -18806,7 +18937,7 @@
       <c r="X668" s="1"/>
       <c r="Y668" s="1"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -18833,7 +18964,7 @@
       <c r="X669" s="1"/>
       <c r="Y669" s="1"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -18860,7 +18991,7 @@
       <c r="X670" s="1"/>
       <c r="Y670" s="1"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -18887,7 +19018,7 @@
       <c r="X671" s="1"/>
       <c r="Y671" s="1"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -18914,7 +19045,7 @@
       <c r="X672" s="1"/>
       <c r="Y672" s="1"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -18941,7 +19072,7 @@
       <c r="X673" s="1"/>
       <c r="Y673" s="1"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -18968,7 +19099,7 @@
       <c r="X674" s="1"/>
       <c r="Y674" s="1"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -18995,7 +19126,7 @@
       <c r="X675" s="1"/>
       <c r="Y675" s="1"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -19022,7 +19153,7 @@
       <c r="X676" s="1"/>
       <c r="Y676" s="1"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -19049,7 +19180,7 @@
       <c r="X677" s="1"/>
       <c r="Y677" s="1"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -19076,7 +19207,7 @@
       <c r="X678" s="1"/>
       <c r="Y678" s="1"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -19103,7 +19234,7 @@
       <c r="X679" s="1"/>
       <c r="Y679" s="1"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -19130,7 +19261,7 @@
       <c r="X680" s="1"/>
       <c r="Y680" s="1"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -19157,7 +19288,7 @@
       <c r="X681" s="1"/>
       <c r="Y681" s="1"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -19184,7 +19315,7 @@
       <c r="X682" s="1"/>
       <c r="Y682" s="1"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -19211,7 +19342,7 @@
       <c r="X683" s="1"/>
       <c r="Y683" s="1"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -19238,7 +19369,7 @@
       <c r="X684" s="1"/>
       <c r="Y684" s="1"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -19265,7 +19396,7 @@
       <c r="X685" s="1"/>
       <c r="Y685" s="1"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -19292,7 +19423,7 @@
       <c r="X686" s="1"/>
       <c r="Y686" s="1"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -19319,7 +19450,7 @@
       <c r="X687" s="1"/>
       <c r="Y687" s="1"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -19346,7 +19477,7 @@
       <c r="X688" s="1"/>
       <c r="Y688" s="1"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -19373,7 +19504,7 @@
       <c r="X689" s="1"/>
       <c r="Y689" s="1"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -19400,7 +19531,7 @@
       <c r="X690" s="1"/>
       <c r="Y690" s="1"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -19427,7 +19558,7 @@
       <c r="X691" s="1"/>
       <c r="Y691" s="1"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -19454,7 +19585,7 @@
       <c r="X692" s="1"/>
       <c r="Y692" s="1"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -19481,7 +19612,7 @@
       <c r="X693" s="1"/>
       <c r="Y693" s="1"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -19508,7 +19639,7 @@
       <c r="X694" s="1"/>
       <c r="Y694" s="1"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -19535,7 +19666,7 @@
       <c r="X695" s="1"/>
       <c r="Y695" s="1"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -19562,7 +19693,7 @@
       <c r="X696" s="1"/>
       <c r="Y696" s="1"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -19589,7 +19720,7 @@
       <c r="X697" s="1"/>
       <c r="Y697" s="1"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -19616,7 +19747,7 @@
       <c r="X698" s="1"/>
       <c r="Y698" s="1"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -19643,7 +19774,7 @@
       <c r="X699" s="1"/>
       <c r="Y699" s="1"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -19670,7 +19801,7 @@
       <c r="X700" s="1"/>
       <c r="Y700" s="1"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -19697,7 +19828,7 @@
       <c r="X701" s="1"/>
       <c r="Y701" s="1"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -19724,7 +19855,7 @@
       <c r="X702" s="1"/>
       <c r="Y702" s="1"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -19751,7 +19882,7 @@
       <c r="X703" s="1"/>
       <c r="Y703" s="1"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -19778,7 +19909,7 @@
       <c r="X704" s="1"/>
       <c r="Y704" s="1"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -19805,7 +19936,7 @@
       <c r="X705" s="1"/>
       <c r="Y705" s="1"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -19832,7 +19963,7 @@
       <c r="X706" s="1"/>
       <c r="Y706" s="1"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -19859,7 +19990,7 @@
       <c r="X707" s="1"/>
       <c r="Y707" s="1"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -19886,7 +20017,7 @@
       <c r="X708" s="1"/>
       <c r="Y708" s="1"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -19913,7 +20044,7 @@
       <c r="X709" s="1"/>
       <c r="Y709" s="1"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -19940,7 +20071,7 @@
       <c r="X710" s="1"/>
       <c r="Y710" s="1"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -19967,7 +20098,7 @@
       <c r="X711" s="1"/>
       <c r="Y711" s="1"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -19994,7 +20125,7 @@
       <c r="X712" s="1"/>
       <c r="Y712" s="1"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -20021,7 +20152,7 @@
       <c r="X713" s="1"/>
       <c r="Y713" s="1"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -20048,7 +20179,7 @@
       <c r="X714" s="1"/>
       <c r="Y714" s="1"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -20075,7 +20206,7 @@
       <c r="X715" s="1"/>
       <c r="Y715" s="1"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -20102,7 +20233,7 @@
       <c r="X716" s="1"/>
       <c r="Y716" s="1"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -20129,7 +20260,7 @@
       <c r="X717" s="1"/>
       <c r="Y717" s="1"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -20156,7 +20287,7 @@
       <c r="X718" s="1"/>
       <c r="Y718" s="1"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -20183,7 +20314,7 @@
       <c r="X719" s="1"/>
       <c r="Y719" s="1"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -20210,7 +20341,7 @@
       <c r="X720" s="1"/>
       <c r="Y720" s="1"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -20237,7 +20368,7 @@
       <c r="X721" s="1"/>
       <c r="Y721" s="1"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -20264,7 +20395,7 @@
       <c r="X722" s="1"/>
       <c r="Y722" s="1"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -20291,7 +20422,7 @@
       <c r="X723" s="1"/>
       <c r="Y723" s="1"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -20318,7 +20449,7 @@
       <c r="X724" s="1"/>
       <c r="Y724" s="1"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -20345,7 +20476,7 @@
       <c r="X725" s="1"/>
       <c r="Y725" s="1"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -20372,7 +20503,7 @@
       <c r="X726" s="1"/>
       <c r="Y726" s="1"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -20399,7 +20530,7 @@
       <c r="X727" s="1"/>
       <c r="Y727" s="1"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -20426,7 +20557,7 @@
       <c r="X728" s="1"/>
       <c r="Y728" s="1"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -20453,7 +20584,7 @@
       <c r="X729" s="1"/>
       <c r="Y729" s="1"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -20480,7 +20611,7 @@
       <c r="X730" s="1"/>
       <c r="Y730" s="1"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -20507,7 +20638,7 @@
       <c r="X731" s="1"/>
       <c r="Y731" s="1"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -20534,7 +20665,7 @@
       <c r="X732" s="1"/>
       <c r="Y732" s="1"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -20561,7 +20692,7 @@
       <c r="X733" s="1"/>
       <c r="Y733" s="1"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -20588,7 +20719,7 @@
       <c r="X734" s="1"/>
       <c r="Y734" s="1"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -20615,7 +20746,7 @@
       <c r="X735" s="1"/>
       <c r="Y735" s="1"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -20642,7 +20773,7 @@
       <c r="X736" s="1"/>
       <c r="Y736" s="1"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -20669,7 +20800,7 @@
       <c r="X737" s="1"/>
       <c r="Y737" s="1"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -20696,7 +20827,7 @@
       <c r="X738" s="1"/>
       <c r="Y738" s="1"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -20723,7 +20854,7 @@
       <c r="X739" s="1"/>
       <c r="Y739" s="1"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -20750,7 +20881,7 @@
       <c r="X740" s="1"/>
       <c r="Y740" s="1"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -20777,7 +20908,7 @@
       <c r="X741" s="1"/>
       <c r="Y741" s="1"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -20804,7 +20935,7 @@
       <c r="X742" s="1"/>
       <c r="Y742" s="1"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -20831,7 +20962,7 @@
       <c r="X743" s="1"/>
       <c r="Y743" s="1"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -20858,7 +20989,7 @@
       <c r="X744" s="1"/>
       <c r="Y744" s="1"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -20885,7 +21016,7 @@
       <c r="X745" s="1"/>
       <c r="Y745" s="1"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -20912,7 +21043,7 @@
       <c r="X746" s="1"/>
       <c r="Y746" s="1"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -20939,7 +21070,7 @@
       <c r="X747" s="1"/>
       <c r="Y747" s="1"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -20966,7 +21097,7 @@
       <c r="X748" s="1"/>
       <c r="Y748" s="1"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -20993,7 +21124,7 @@
       <c r="X749" s="1"/>
       <c r="Y749" s="1"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -21020,7 +21151,7 @@
       <c r="X750" s="1"/>
       <c r="Y750" s="1"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -21047,7 +21178,7 @@
       <c r="X751" s="1"/>
       <c r="Y751" s="1"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -21074,7 +21205,7 @@
       <c r="X752" s="1"/>
       <c r="Y752" s="1"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -21101,7 +21232,7 @@
       <c r="X753" s="1"/>
       <c r="Y753" s="1"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -21128,7 +21259,7 @@
       <c r="X754" s="1"/>
       <c r="Y754" s="1"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -21155,7 +21286,7 @@
       <c r="X755" s="1"/>
       <c r="Y755" s="1"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -21182,7 +21313,7 @@
       <c r="X756" s="1"/>
       <c r="Y756" s="1"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -21209,7 +21340,7 @@
       <c r="X757" s="1"/>
       <c r="Y757" s="1"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -21236,7 +21367,7 @@
       <c r="X758" s="1"/>
       <c r="Y758" s="1"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -21263,7 +21394,7 @@
       <c r="X759" s="1"/>
       <c r="Y759" s="1"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -21290,7 +21421,7 @@
       <c r="X760" s="1"/>
       <c r="Y760" s="1"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -21317,7 +21448,7 @@
       <c r="X761" s="1"/>
       <c r="Y761" s="1"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -21344,7 +21475,7 @@
       <c r="X762" s="1"/>
       <c r="Y762" s="1"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -21371,7 +21502,7 @@
       <c r="X763" s="1"/>
       <c r="Y763" s="1"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -21398,7 +21529,7 @@
       <c r="X764" s="1"/>
       <c r="Y764" s="1"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -21425,7 +21556,7 @@
       <c r="X765" s="1"/>
       <c r="Y765" s="1"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -21452,7 +21583,7 @@
       <c r="X766" s="1"/>
       <c r="Y766" s="1"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -21479,7 +21610,7 @@
       <c r="X767" s="1"/>
       <c r="Y767" s="1"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -21506,7 +21637,7 @@
       <c r="X768" s="1"/>
       <c r="Y768" s="1"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -21533,7 +21664,7 @@
       <c r="X769" s="1"/>
       <c r="Y769" s="1"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -21560,7 +21691,7 @@
       <c r="X770" s="1"/>
       <c r="Y770" s="1"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -21587,7 +21718,7 @@
       <c r="X771" s="1"/>
       <c r="Y771" s="1"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -21614,7 +21745,7 @@
       <c r="X772" s="1"/>
       <c r="Y772" s="1"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -21641,7 +21772,7 @@
       <c r="X773" s="1"/>
       <c r="Y773" s="1"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -21668,7 +21799,7 @@
       <c r="X774" s="1"/>
       <c r="Y774" s="1"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -21695,7 +21826,7 @@
       <c r="X775" s="1"/>
       <c r="Y775" s="1"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -21722,7 +21853,7 @@
       <c r="X776" s="1"/>
       <c r="Y776" s="1"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -21749,7 +21880,7 @@
       <c r="X777" s="1"/>
       <c r="Y777" s="1"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -21776,7 +21907,7 @@
       <c r="X778" s="1"/>
       <c r="Y778" s="1"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -21803,7 +21934,7 @@
       <c r="X779" s="1"/>
       <c r="Y779" s="1"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -21830,7 +21961,7 @@
       <c r="X780" s="1"/>
       <c r="Y780" s="1"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -21857,7 +21988,7 @@
       <c r="X781" s="1"/>
       <c r="Y781" s="1"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -21884,7 +22015,7 @@
       <c r="X782" s="1"/>
       <c r="Y782" s="1"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -21911,7 +22042,7 @@
       <c r="X783" s="1"/>
       <c r="Y783" s="1"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -21938,7 +22069,7 @@
       <c r="X784" s="1"/>
       <c r="Y784" s="1"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -21965,7 +22096,7 @@
       <c r="X785" s="1"/>
       <c r="Y785" s="1"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -21992,7 +22123,7 @@
       <c r="X786" s="1"/>
       <c r="Y786" s="1"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -22019,7 +22150,7 @@
       <c r="X787" s="1"/>
       <c r="Y787" s="1"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -22046,7 +22177,7 @@
       <c r="X788" s="1"/>
       <c r="Y788" s="1"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -22073,7 +22204,7 @@
       <c r="X789" s="1"/>
       <c r="Y789" s="1"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -22100,7 +22231,7 @@
       <c r="X790" s="1"/>
       <c r="Y790" s="1"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -22127,7 +22258,7 @@
       <c r="X791" s="1"/>
       <c r="Y791" s="1"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -22154,7 +22285,7 @@
       <c r="X792" s="1"/>
       <c r="Y792" s="1"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -22181,7 +22312,7 @@
       <c r="X793" s="1"/>
       <c r="Y793" s="1"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -22208,7 +22339,7 @@
       <c r="X794" s="1"/>
       <c r="Y794" s="1"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -22235,7 +22366,7 @@
       <c r="X795" s="1"/>
       <c r="Y795" s="1"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -22262,7 +22393,7 @@
       <c r="X796" s="1"/>
       <c r="Y796" s="1"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -22289,7 +22420,7 @@
       <c r="X797" s="1"/>
       <c r="Y797" s="1"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -22316,7 +22447,7 @@
       <c r="X798" s="1"/>
       <c r="Y798" s="1"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -22343,7 +22474,7 @@
       <c r="X799" s="1"/>
       <c r="Y799" s="1"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -22370,7 +22501,7 @@
       <c r="X800" s="1"/>
       <c r="Y800" s="1"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -22397,7 +22528,7 @@
       <c r="X801" s="1"/>
       <c r="Y801" s="1"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -22424,7 +22555,7 @@
       <c r="X802" s="1"/>
       <c r="Y802" s="1"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -22451,7 +22582,7 @@
       <c r="X803" s="1"/>
       <c r="Y803" s="1"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -22478,7 +22609,7 @@
       <c r="X804" s="1"/>
       <c r="Y804" s="1"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -22505,7 +22636,7 @@
       <c r="X805" s="1"/>
       <c r="Y805" s="1"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -22532,7 +22663,7 @@
       <c r="X806" s="1"/>
       <c r="Y806" s="1"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -22559,7 +22690,7 @@
       <c r="X807" s="1"/>
       <c r="Y807" s="1"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -22586,7 +22717,7 @@
       <c r="X808" s="1"/>
       <c r="Y808" s="1"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -22613,7 +22744,7 @@
       <c r="X809" s="1"/>
       <c r="Y809" s="1"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -22640,7 +22771,7 @@
       <c r="X810" s="1"/>
       <c r="Y810" s="1"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -22667,7 +22798,7 @@
       <c r="X811" s="1"/>
       <c r="Y811" s="1"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -22694,7 +22825,7 @@
       <c r="X812" s="1"/>
       <c r="Y812" s="1"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -22721,7 +22852,7 @@
       <c r="X813" s="1"/>
       <c r="Y813" s="1"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -22748,7 +22879,7 @@
       <c r="X814" s="1"/>
       <c r="Y814" s="1"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -22775,7 +22906,7 @@
       <c r="X815" s="1"/>
       <c r="Y815" s="1"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -22802,7 +22933,7 @@
       <c r="X816" s="1"/>
       <c r="Y816" s="1"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -22829,7 +22960,7 @@
       <c r="X817" s="1"/>
       <c r="Y817" s="1"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -22856,7 +22987,7 @@
       <c r="X818" s="1"/>
       <c r="Y818" s="1"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -22883,7 +23014,7 @@
       <c r="X819" s="1"/>
       <c r="Y819" s="1"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -22910,7 +23041,7 @@
       <c r="X820" s="1"/>
       <c r="Y820" s="1"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -22937,7 +23068,7 @@
       <c r="X821" s="1"/>
       <c r="Y821" s="1"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -22964,7 +23095,7 @@
       <c r="X822" s="1"/>
       <c r="Y822" s="1"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -22991,7 +23122,7 @@
       <c r="X823" s="1"/>
       <c r="Y823" s="1"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -23018,7 +23149,7 @@
       <c r="X824" s="1"/>
       <c r="Y824" s="1"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -23045,7 +23176,7 @@
       <c r="X825" s="1"/>
       <c r="Y825" s="1"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -23072,7 +23203,7 @@
       <c r="X826" s="1"/>
       <c r="Y826" s="1"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -23099,7 +23230,7 @@
       <c r="X827" s="1"/>
       <c r="Y827" s="1"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -23126,7 +23257,7 @@
       <c r="X828" s="1"/>
       <c r="Y828" s="1"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -23153,7 +23284,7 @@
       <c r="X829" s="1"/>
       <c r="Y829" s="1"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -23180,7 +23311,7 @@
       <c r="X830" s="1"/>
       <c r="Y830" s="1"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -23207,7 +23338,7 @@
       <c r="X831" s="1"/>
       <c r="Y831" s="1"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -23234,7 +23365,7 @@
       <c r="X832" s="1"/>
       <c r="Y832" s="1"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -23261,7 +23392,7 @@
       <c r="X833" s="1"/>
       <c r="Y833" s="1"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -23288,7 +23419,7 @@
       <c r="X834" s="1"/>
       <c r="Y834" s="1"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -23315,7 +23446,7 @@
       <c r="X835" s="1"/>
       <c r="Y835" s="1"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -23342,7 +23473,7 @@
       <c r="X836" s="1"/>
       <c r="Y836" s="1"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -23369,7 +23500,7 @@
       <c r="X837" s="1"/>
       <c r="Y837" s="1"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -23396,7 +23527,7 @@
       <c r="X838" s="1"/>
       <c r="Y838" s="1"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -23423,7 +23554,7 @@
       <c r="X839" s="1"/>
       <c r="Y839" s="1"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -23450,7 +23581,7 @@
       <c r="X840" s="1"/>
       <c r="Y840" s="1"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -23477,7 +23608,7 @@
       <c r="X841" s="1"/>
       <c r="Y841" s="1"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -23504,7 +23635,7 @@
       <c r="X842" s="1"/>
       <c r="Y842" s="1"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -23531,7 +23662,7 @@
       <c r="X843" s="1"/>
       <c r="Y843" s="1"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -23558,7 +23689,7 @@
       <c r="X844" s="1"/>
       <c r="Y844" s="1"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -23585,7 +23716,7 @@
       <c r="X845" s="1"/>
       <c r="Y845" s="1"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -23612,7 +23743,7 @@
       <c r="X846" s="1"/>
       <c r="Y846" s="1"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -23639,7 +23770,7 @@
       <c r="X847" s="1"/>
       <c r="Y847" s="1"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -23666,7 +23797,7 @@
       <c r="X848" s="1"/>
       <c r="Y848" s="1"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -23693,7 +23824,7 @@
       <c r="X849" s="1"/>
       <c r="Y849" s="1"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -23720,7 +23851,7 @@
       <c r="X850" s="1"/>
       <c r="Y850" s="1"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -23747,7 +23878,7 @@
       <c r="X851" s="1"/>
       <c r="Y851" s="1"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -23774,7 +23905,7 @@
       <c r="X852" s="1"/>
       <c r="Y852" s="1"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -23801,7 +23932,7 @@
       <c r="X853" s="1"/>
       <c r="Y853" s="1"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -23828,7 +23959,7 @@
       <c r="X854" s="1"/>
       <c r="Y854" s="1"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -23855,7 +23986,7 @@
       <c r="X855" s="1"/>
       <c r="Y855" s="1"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -23882,7 +24013,7 @@
       <c r="X856" s="1"/>
       <c r="Y856" s="1"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -23909,7 +24040,7 @@
       <c r="X857" s="1"/>
       <c r="Y857" s="1"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -23936,7 +24067,7 @@
       <c r="X858" s="1"/>
       <c r="Y858" s="1"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -23963,7 +24094,7 @@
       <c r="X859" s="1"/>
       <c r="Y859" s="1"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -23990,7 +24121,7 @@
       <c r="X860" s="1"/>
       <c r="Y860" s="1"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -24017,7 +24148,7 @@
       <c r="X861" s="1"/>
       <c r="Y861" s="1"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -24044,7 +24175,7 @@
       <c r="X862" s="1"/>
       <c r="Y862" s="1"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -24071,7 +24202,7 @@
       <c r="X863" s="1"/>
       <c r="Y863" s="1"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -24098,7 +24229,7 @@
       <c r="X864" s="1"/>
       <c r="Y864" s="1"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -24125,7 +24256,7 @@
       <c r="X865" s="1"/>
       <c r="Y865" s="1"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -24152,7 +24283,7 @@
       <c r="X866" s="1"/>
       <c r="Y866" s="1"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -24179,7 +24310,7 @@
       <c r="X867" s="1"/>
       <c r="Y867" s="1"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -24206,7 +24337,7 @@
       <c r="X868" s="1"/>
       <c r="Y868" s="1"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -24233,7 +24364,7 @@
       <c r="X869" s="1"/>
       <c r="Y869" s="1"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -24260,7 +24391,7 @@
       <c r="X870" s="1"/>
       <c r="Y870" s="1"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -24287,7 +24418,7 @@
       <c r="X871" s="1"/>
       <c r="Y871" s="1"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -24314,7 +24445,7 @@
       <c r="X872" s="1"/>
       <c r="Y872" s="1"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -24341,7 +24472,7 @@
       <c r="X873" s="1"/>
       <c r="Y873" s="1"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -24368,7 +24499,7 @@
       <c r="X874" s="1"/>
       <c r="Y874" s="1"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -24395,7 +24526,7 @@
       <c r="X875" s="1"/>
       <c r="Y875" s="1"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -24422,7 +24553,7 @@
       <c r="X876" s="1"/>
       <c r="Y876" s="1"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -24449,7 +24580,7 @@
       <c r="X877" s="1"/>
       <c r="Y877" s="1"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -24476,7 +24607,7 @@
       <c r="X878" s="1"/>
       <c r="Y878" s="1"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -24503,7 +24634,7 @@
       <c r="X879" s="1"/>
       <c r="Y879" s="1"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -24530,7 +24661,7 @@
       <c r="X880" s="1"/>
       <c r="Y880" s="1"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -24557,7 +24688,7 @@
       <c r="X881" s="1"/>
       <c r="Y881" s="1"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -24584,7 +24715,7 @@
       <c r="X882" s="1"/>
       <c r="Y882" s="1"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -24611,7 +24742,7 @@
       <c r="X883" s="1"/>
       <c r="Y883" s="1"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -24638,7 +24769,7 @@
       <c r="X884" s="1"/>
       <c r="Y884" s="1"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -24665,7 +24796,7 @@
       <c r="X885" s="1"/>
       <c r="Y885" s="1"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -24692,7 +24823,7 @@
       <c r="X886" s="1"/>
       <c r="Y886" s="1"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -24719,7 +24850,7 @@
       <c r="X887" s="1"/>
       <c r="Y887" s="1"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -24746,7 +24877,7 @@
       <c r="X888" s="1"/>
       <c r="Y888" s="1"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -24773,7 +24904,7 @@
       <c r="X889" s="1"/>
       <c r="Y889" s="1"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -24800,7 +24931,7 @@
       <c r="X890" s="1"/>
       <c r="Y890" s="1"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -24827,7 +24958,7 @@
       <c r="X891" s="1"/>
       <c r="Y891" s="1"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -24854,7 +24985,7 @@
       <c r="X892" s="1"/>
       <c r="Y892" s="1"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -24881,7 +25012,7 @@
       <c r="X893" s="1"/>
       <c r="Y893" s="1"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -24908,7 +25039,7 @@
       <c r="X894" s="1"/>
       <c r="Y894" s="1"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -24935,7 +25066,7 @@
       <c r="X895" s="1"/>
       <c r="Y895" s="1"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -24962,7 +25093,7 @@
       <c r="X896" s="1"/>
       <c r="Y896" s="1"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -24989,7 +25120,7 @@
       <c r="X897" s="1"/>
       <c r="Y897" s="1"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -25016,7 +25147,7 @@
       <c r="X898" s="1"/>
       <c r="Y898" s="1"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -25043,7 +25174,7 @@
       <c r="X899" s="1"/>
       <c r="Y899" s="1"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -25070,7 +25201,7 @@
       <c r="X900" s="1"/>
       <c r="Y900" s="1"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -25097,7 +25228,7 @@
       <c r="X901" s="1"/>
       <c r="Y901" s="1"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -25124,7 +25255,7 @@
       <c r="X902" s="1"/>
       <c r="Y902" s="1"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -25151,7 +25282,7 @@
       <c r="X903" s="1"/>
       <c r="Y903" s="1"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -25178,7 +25309,7 @@
       <c r="X904" s="1"/>
       <c r="Y904" s="1"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -25205,7 +25336,7 @@
       <c r="X905" s="1"/>
       <c r="Y905" s="1"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -25232,7 +25363,7 @@
       <c r="X906" s="1"/>
       <c r="Y906" s="1"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -25259,7 +25390,7 @@
       <c r="X907" s="1"/>
       <c r="Y907" s="1"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -25286,7 +25417,7 @@
       <c r="X908" s="1"/>
       <c r="Y908" s="1"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -25313,7 +25444,7 @@
       <c r="X909" s="1"/>
       <c r="Y909" s="1"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -25340,7 +25471,7 @@
       <c r="X910" s="1"/>
       <c r="Y910" s="1"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -25367,7 +25498,7 @@
       <c r="X911" s="1"/>
       <c r="Y911" s="1"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -25394,7 +25525,7 @@
       <c r="X912" s="1"/>
       <c r="Y912" s="1"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -25421,7 +25552,7 @@
       <c r="X913" s="1"/>
       <c r="Y913" s="1"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -25448,7 +25579,7 @@
       <c r="X914" s="1"/>
       <c r="Y914" s="1"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -25475,7 +25606,7 @@
       <c r="X915" s="1"/>
       <c r="Y915" s="1"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -25502,7 +25633,7 @@
       <c r="X916" s="1"/>
       <c r="Y916" s="1"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -25529,7 +25660,7 @@
       <c r="X917" s="1"/>
       <c r="Y917" s="1"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -25556,7 +25687,7 @@
       <c r="X918" s="1"/>
       <c r="Y918" s="1"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -25583,7 +25714,7 @@
       <c r="X919" s="1"/>
       <c r="Y919" s="1"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -25610,7 +25741,7 @@
       <c r="X920" s="1"/>
       <c r="Y920" s="1"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -25637,7 +25768,7 @@
       <c r="X921" s="1"/>
       <c r="Y921" s="1"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -25664,7 +25795,7 @@
       <c r="X922" s="1"/>
       <c r="Y922" s="1"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -25691,7 +25822,7 @@
       <c r="X923" s="1"/>
       <c r="Y923" s="1"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -25718,7 +25849,7 @@
       <c r="X924" s="1"/>
       <c r="Y924" s="1"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -25745,7 +25876,7 @@
       <c r="X925" s="1"/>
       <c r="Y925" s="1"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -25772,7 +25903,7 @@
       <c r="X926" s="1"/>
       <c r="Y926" s="1"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -25799,7 +25930,7 @@
       <c r="X927" s="1"/>
       <c r="Y927" s="1"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -25826,7 +25957,7 @@
       <c r="X928" s="1"/>
       <c r="Y928" s="1"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -25853,7 +25984,7 @@
       <c r="X929" s="1"/>
       <c r="Y929" s="1"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -25880,7 +26011,7 @@
       <c r="X930" s="1"/>
       <c r="Y930" s="1"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -25907,7 +26038,7 @@
       <c r="X931" s="1"/>
       <c r="Y931" s="1"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -25934,7 +26065,7 @@
       <c r="X932" s="1"/>
       <c r="Y932" s="1"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -25961,7 +26092,7 @@
       <c r="X933" s="1"/>
       <c r="Y933" s="1"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -25988,7 +26119,7 @@
       <c r="X934" s="1"/>
       <c r="Y934" s="1"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -26015,7 +26146,7 @@
       <c r="X935" s="1"/>
       <c r="Y935" s="1"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -26042,7 +26173,7 @@
       <c r="X936" s="1"/>
       <c r="Y936" s="1"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -26069,7 +26200,7 @@
       <c r="X937" s="1"/>
       <c r="Y937" s="1"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -26096,7 +26227,7 @@
       <c r="X938" s="1"/>
       <c r="Y938" s="1"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -26123,7 +26254,7 @@
       <c r="X939" s="1"/>
       <c r="Y939" s="1"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -26150,7 +26281,7 @@
       <c r="X940" s="1"/>
       <c r="Y940" s="1"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -26177,7 +26308,7 @@
       <c r="X941" s="1"/>
       <c r="Y941" s="1"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -26204,7 +26335,7 @@
       <c r="X942" s="1"/>
       <c r="Y942" s="1"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -26231,7 +26362,7 @@
       <c r="X943" s="1"/>
       <c r="Y943" s="1"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -26258,7 +26389,7 @@
       <c r="X944" s="1"/>
       <c r="Y944" s="1"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -26285,7 +26416,7 @@
       <c r="X945" s="1"/>
       <c r="Y945" s="1"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -26312,7 +26443,7 @@
       <c r="X946" s="1"/>
       <c r="Y946" s="1"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -26339,7 +26470,7 @@
       <c r="X947" s="1"/>
       <c r="Y947" s="1"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -26366,7 +26497,7 @@
       <c r="X948" s="1"/>
       <c r="Y948" s="1"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -26393,7 +26524,7 @@
       <c r="X949" s="1"/>
       <c r="Y949" s="1"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -26420,7 +26551,7 @@
       <c r="X950" s="1"/>
       <c r="Y950" s="1"/>
     </row>
-    <row r="951">
+    <row r="951" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -26447,7 +26578,7 @@
       <c r="X951" s="1"/>
       <c r="Y951" s="1"/>
     </row>
-    <row r="952">
+    <row r="952" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -26474,7 +26605,7 @@
       <c r="X952" s="1"/>
       <c r="Y952" s="1"/>
     </row>
-    <row r="953">
+    <row r="953" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -26501,7 +26632,7 @@
       <c r="X953" s="1"/>
       <c r="Y953" s="1"/>
     </row>
-    <row r="954">
+    <row r="954" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -26528,7 +26659,7 @@
       <c r="X954" s="1"/>
       <c r="Y954" s="1"/>
     </row>
-    <row r="955">
+    <row r="955" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -26555,7 +26686,7 @@
       <c r="X955" s="1"/>
       <c r="Y955" s="1"/>
     </row>
-    <row r="956">
+    <row r="956" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -26582,7 +26713,7 @@
       <c r="X956" s="1"/>
       <c r="Y956" s="1"/>
     </row>
-    <row r="957">
+    <row r="957" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -26609,7 +26740,7 @@
       <c r="X957" s="1"/>
       <c r="Y957" s="1"/>
     </row>
-    <row r="958">
+    <row r="958" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -26636,7 +26767,7 @@
       <c r="X958" s="1"/>
       <c r="Y958" s="1"/>
     </row>
-    <row r="959">
+    <row r="959" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -26663,7 +26794,7 @@
       <c r="X959" s="1"/>
       <c r="Y959" s="1"/>
     </row>
-    <row r="960">
+    <row r="960" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -26690,7 +26821,7 @@
       <c r="X960" s="1"/>
       <c r="Y960" s="1"/>
     </row>
-    <row r="961">
+    <row r="961" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -26717,7 +26848,7 @@
       <c r="X961" s="1"/>
       <c r="Y961" s="1"/>
     </row>
-    <row r="962">
+    <row r="962" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -26744,7 +26875,7 @@
       <c r="X962" s="1"/>
       <c r="Y962" s="1"/>
     </row>
-    <row r="963">
+    <row r="963" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -26771,7 +26902,7 @@
       <c r="X963" s="1"/>
       <c r="Y963" s="1"/>
     </row>
-    <row r="964">
+    <row r="964" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -26798,7 +26929,7 @@
       <c r="X964" s="1"/>
       <c r="Y964" s="1"/>
     </row>
-    <row r="965">
+    <row r="965" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -26825,7 +26956,7 @@
       <c r="X965" s="1"/>
       <c r="Y965" s="1"/>
     </row>
-    <row r="966">
+    <row r="966" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -26852,7 +26983,7 @@
       <c r="X966" s="1"/>
       <c r="Y966" s="1"/>
     </row>
-    <row r="967">
+    <row r="967" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -26879,7 +27010,7 @@
       <c r="X967" s="1"/>
       <c r="Y967" s="1"/>
     </row>
-    <row r="968">
+    <row r="968" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -26906,7 +27037,7 @@
       <c r="X968" s="1"/>
       <c r="Y968" s="1"/>
     </row>
-    <row r="969">
+    <row r="969" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -26933,7 +27064,7 @@
       <c r="X969" s="1"/>
       <c r="Y969" s="1"/>
     </row>
-    <row r="970">
+    <row r="970" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -26960,7 +27091,7 @@
       <c r="X970" s="1"/>
       <c r="Y970" s="1"/>
     </row>
-    <row r="971">
+    <row r="971" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -26987,7 +27118,7 @@
       <c r="X971" s="1"/>
       <c r="Y971" s="1"/>
     </row>
-    <row r="972">
+    <row r="972" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -27014,7 +27145,7 @@
       <c r="X972" s="1"/>
       <c r="Y972" s="1"/>
     </row>
-    <row r="973">
+    <row r="973" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -27041,7 +27172,7 @@
       <c r="X973" s="1"/>
       <c r="Y973" s="1"/>
     </row>
-    <row r="974">
+    <row r="974" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -27068,7 +27199,7 @@
       <c r="X974" s="1"/>
       <c r="Y974" s="1"/>
     </row>
-    <row r="975">
+    <row r="975" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -27095,7 +27226,7 @@
       <c r="X975" s="1"/>
       <c r="Y975" s="1"/>
     </row>
-    <row r="976">
+    <row r="976" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -27122,13 +27253,39 @@
       <c r="X976" s="1"/>
       <c r="Y976" s="1"/>
     </row>
+    <row r="977" spans="1:25" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A977" s="1"/>
+      <c r="B977" s="1"/>
+      <c r="C977" s="1"/>
+      <c r="D977" s="1"/>
+      <c r="E977" s="1"/>
+      <c r="F977" s="1"/>
+      <c r="G977" s="1"/>
+      <c r="H977" s="1"/>
+      <c r="I977" s="1"/>
+      <c r="J977" s="1"/>
+      <c r="K977" s="1"/>
+      <c r="L977" s="1"/>
+      <c r="M977" s="1"/>
+      <c r="N977" s="1"/>
+      <c r="O977" s="1"/>
+      <c r="P977" s="1"/>
+      <c r="Q977" s="1"/>
+      <c r="R977" s="1"/>
+      <c r="S977" s="1"/>
+      <c r="T977" s="1"/>
+      <c r="U977" s="1"/>
+      <c r="V977" s="1"/>
+      <c r="W977" s="1"/>
+      <c r="X977" s="1"/>
+      <c r="Y977" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A32:A35"/>
   </mergeCells>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="portrait" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
 </worksheet>
 </file>